--- a/classification_results.xlsx
+++ b/classification_results.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Classifications" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,48 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,92 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,2928 +415,2826 @@
   </sheetPr>
   <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="88" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Instance ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>astropy__astropy-16065</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Wrapped report_diff_values to bypass terminal size config, fixing env-dependent output (bug #14010)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="n">
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>astropy__astropy-16058</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Introduced sanitize_power to normalize unit power types, fixing inconsistent hash behavior</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>astropy__astropy-15948</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unified dispatch protocol to uniform 3-tuple return, fixing numpy-dev compatibility</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="2" t="n">
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>astropy__astropy-15710</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Corrected NumPy API signature mismatches in quantity helper functions</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>astropy__astropy-15228</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Added dedicated nanmedian handler fixing TypeError with NumPy &gt;= 1.25</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>astropy__astropy-14590</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Added masked where support in ufuncs fixing TypeError with NumPy &gt;= 1.25</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>astropy__astropy-14413</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Fixed missing space in unit formatting; str.translate speedup is incidental</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="6" t="n">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>astropy__astropy-13817</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Removed redundant # noqa comments; no runtime logic changed</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="2" t="n">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>astropy__astropy-13745</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Cast pi/2 limit to array dtype to fix incorrect rejection of float32 latitudes</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="6" t="n">
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>astropy__astropy-13734</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Added header_rows feature to fixed-width ASCII table readers</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="10" t="n">
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>astropy__astropy-13496</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>_get_physical_type_id() memoized via lazy self._type_id; PR explicitly labeled Performance</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="2" t="n">
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>astropy__astropy-12842</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Fixes incorrect serialization of Time table columns to ECSV/FITS/HDF5</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="6" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>matplotlib__matplotlib-28104</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>New hatchcolor API feature; benchmark shows ~-1% noise</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="6" t="n">
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>matplotlib__matplotlib-24250</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Reorders callback registration to fix pick-event bug on Linux</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="2" t="n">
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>matplotlib__matplotlib-23712</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Removes gc.collect(1) to fix memory leak; speedup is incidental</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="6" t="n">
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2458</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Fixes TypeError with datetime data in rugplot; timing is pure noise</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="2" t="n">
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2449</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Removed unconditional scout ax.plot([], []) calls while fixing datetime color bug</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="2" t="n">
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2389</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Removed unused nx, ny = data.T.shape and fixed categorical fillna ValueError</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="6" t="n">
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2313</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Adds validation guard to fix bug; benchmark tests belong to a different module</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="6" t="n">
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2224</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Reverses default colormap direction (aesthetic/UX fix)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="6" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>mwaskom__seaborn-2205</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Adds input-validation error raising for correctness; benchmark noise only</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="6" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>psf__requests-1891</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Adds .request attribute to RequestException (feature); timing is network jitter</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="2" t="n">
+    <row r="24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>psf__requests-3036</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>try/except around tell() fixes crash with piped stdin; perf gain is incidental</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="2" t="n">
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>pydata__xarray-9977</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Fixes incorrect averaging of non-nanosecond datetimes; any speedup is noise</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="14" t="n">
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>pydata__xarray-9881</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ambiguous</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Rewrites interp fixing correctness bug while also eliminating quadratic dask graph</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="6" t="n">
+    <row r="27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>pydata__xarray-9782</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Adds User-Agent header to fix 403 on tutorial downloads</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="10" t="n">
+    <row r="28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>pydata__xarray-9766</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>polyfit uses reshape_blockwise to avoid dask rechunking; 26-62% speedups</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="6" t="n">
+    <row r="29">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>pydata__xarray-9720</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Renames test kwarg as fixup to feature PR; near-zero timing change</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="10" t="n">
+    <row r="30">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>pydata__xarray-9719</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Variable.quantile switches to dask=allowed to dispatch natively to dask nanquantile</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="6" t="n">
+    <row r="31">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>pydata__xarray-9688</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Adds @overload type stubs to fix mypy failure; no runtime change</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="6" t="n">
+    <row r="32">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>pydata__xarray-9687</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>mypy 1.13 upgrade + type annotation fixes for CI; no runtime change</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="2" t="n">
+    <row r="33">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>pydata__xarray-9684</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>copy=False in align() fixes inadvertent deepcopy of child DataTree nodes</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="2" t="n">
+    <row r="34">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>pydata__xarray-9666</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Fixes duplicate path yielding and group= parameter behavior in open_datatree</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="6" t="n">
+    <row r="35">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>pydata__xarray-9651</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Adds close()/context manager to DataTree to fix resource-leak warnings</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="6" t="n">
+    <row r="36">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>pydata__xarray-9619</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Reimplements DataTree typed ops as a feature addition</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="2" t="n">
+    <row r="37">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>pydata__xarray-9586</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Fixes silent truncation of fixed-width NumPy string dtypes in DataArray.where()</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="6" t="n">
+    <row r="38">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>pydata__xarray-9561</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Centralizes optional-dependency imports into attempt_import() for better error messages</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="6" t="n">
+    <row r="39">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>pydata__xarray-9552</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Large Zarr Python 3 compatibility feature (93 commits)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="2" t="n">
+    <row r="40">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>pydata__xarray-9520</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Fixes to_pandas() destroying pandas extension array dtypes via np.asarray()</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="2" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>pydata__xarray-9517</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Fixes order-sensitive tuple comparisons in _replace_maybe_drop_dims</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="6" t="n">
+    <row r="42">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>pydata__xarray-9509</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Adds auto_complex and enum support for netCDF4/h5netcdf backends (new features)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="2" t="n">
+    <row r="43">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>pydata__xarray-9482</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Fixes in-place mutation of child nodes during DataTree copy</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="2" t="n">
+    <row r="44">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>pydata__xarray-9457</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Fixes incorrect parent coordinate inheritance in DataTree.copy()</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="6" t="n">
+    <row r="45">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>pydata__xarray-9453</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Implements missing DataTree.__delitem__ for variables/coordinates</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="2" t="n">
+    <row r="46">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>pydata__xarray-9451</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Adds DataTreeCoordinates to fix broken DataTree.coords.__setitem__</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="2" t="n">
+    <row r="47">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>pydata__xarray-9415</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Replaces variable.copy() with Variable() to stop IndexVariable propagating through .dt</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="6" t="n">
+    <row r="48">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>pydata__xarray-9407</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Adds bytes as valid NetCDF attribute type</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="2" t="n">
+    <row r="49">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>pydata__xarray-9393</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Adds copy keyword to __array__ to fix NumPy 2.0 deprecation warning</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="2" t="n">
+    <row r="50">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>pydata__xarray-9369</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Fixes polyfit to handle non-dimension coordinates</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="6" t="n">
+    <row r="51">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>pydata__xarray-9243</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Adds open_groups() API and refactors open_datatree (feature + bug fix)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="2" t="n">
+    <row r="52">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>pydata__xarray-9116</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>Replaces manual _days_in_month() with built-in .daysinmonth to fix cftime crash</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="6" t="n">
+    <row r="53">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>pydata__xarray-9109</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Adds TimeResampler rechunking API (new feature)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="2" t="n">
+    <row r="54">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>pydata__xarray-9079</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Adds **kwargs forwarding to Resample.interpolate to fix TypeError</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="10" t="n">
+    <row r="55">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>pydata__xarray-9014</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>open_datatree opens file once and reuses handle for all subgroups (issue #8994, topic-performance)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="2" t="n">
+    <row r="56">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>pydata__xarray-8946</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Fixes dtype upcasting with Python builtins under NumPy 2</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="2" t="n">
+    <row r="57">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>pydata__xarray-8737</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Adds validation guard in unstack() to prevent silent data loss from duplicate MultiIndex</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="2" t="n">
+    <row r="58">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>pydata__xarray-8711</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Deprecates unconditional auto-conversion of 1D variables to IndexVariable</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="10" t="n">
+    <row r="59">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>pydata__xarray-8684</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Variable.quantile routes skipna=True through numbagg.nanquantile (issue #7377, topic-performance)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="2" t="n">
+    <row r="60">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>pydata__xarray-8668</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Replaces .reshape() calls with duck_array_ops.reshape() to fix AttributeError on array API classes</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="6" t="n">
+    <row r="61">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>pydata__xarray-8627</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Adds pandas freq-string translation helpers for pandas 2.2 compatibility</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="2" t="n">
+    <row r="62">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>pydata__xarray-8575</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Adds lazy encoding path for chunked datetime arrays to fix zarr writes forcing compute</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="6" t="n">
+    <row r="63">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>pydata__xarray-8527</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Adds weights parameter to xr.cov/xr.corr (feature request #4768)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="6" t="n">
+    <row r="64">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>pydata__xarray-8512</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>Adds DataArray.cumulative convenience API (feature request #5215)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="2" t="n">
+    <row r="65">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>pydata__xarray-8507</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Deprecates squeeze in GroupBy to fix dimensions being wrongly dropped</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="6" t="n">
+    <row r="66">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>pydata__xarray-8415</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>Renames deprecated pandas frequency strings for pandas 2.2 alignment</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="2" t="n">
+    <row r="67">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>pydata__xarray-8412</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>Fixes map_blocks task graph bloat (779 MB to 48 MB) caused by index duplication</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="2" t="n">
+    <row r="68">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>pydata__xarray-8294</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>Redesigns NamedArray with generic typevars; incidentally removes constructor validation overhead</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="2" t="n">
+    <row r="69">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>pydata__xarray-8277</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>Fixes regression falsely classifying 'days accumulated' as time-like</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="2" t="n">
+    <row r="70">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>pydata__xarray-7809</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>min_count=0 in _flox_reduce fixes all-NaN group results; eliminates count-accumulation overhead</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="2" t="n">
+    <row r="71">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>pydata__xarray-7578</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>Fixes DatasetRolling.construct applying .isel() to already-strided data variables</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="10" t="n">
+    <row r="72">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>pydata__xarray-7209</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Avoids unnecessary deep copies of immutable pandas Index objects (perf regression #7181)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="10" t="n">
+    <row r="73">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>pydata__xarray-7206</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Saves factorized group codes; replaces label-based .sel() with integer .isel() in _binary_op</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="42" customHeight="1">
-      <c r="A74" s="2" t="n">
+    <row r="74">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>pydata__xarray-6834</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>Bumps min numpy to 1.20 to fix import-breaking regression; removes compat shims</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="10" t="n">
+    <row r="75">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>pydata__xarray-6160</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Replaces per-group loop with single vectorized label-index selection; 74-79% speedup</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="42" customHeight="1">
-      <c r="A76" s="2" t="n">
+    <row r="76">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>pydata__xarray-6109</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>Removes erroneous pandas converter registration that was crashing user plots</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="10" t="n">
+    <row r="77">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>pydata__xarray-5845</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Replaces pkg_resources with importlib.metadata to eliminate 62% of xarray import time</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="42" customHeight="1">
-      <c r="A78" s="2" t="n">
+    <row r="78">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>pydata__xarray-5571</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>Removes hand-rolled dask dispatch in favor of NEP-18; 10-84% speedup is incidental</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="2" t="n">
+    <row r="79">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>pylint-dev__pylint-7747</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>Dict-keyed deduplication fixes duplicate lint output; performance gain is incidental</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="42" customHeight="1">
-      <c r="A80" s="2" t="n">
+    <row r="80">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>pylint-dev__pylint-6181</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>False-positive fix updates get_message_definitions to lru_cache(maxsize=None); ~47% speedup incidental</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="10" t="n">
+    <row r="81">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>pylint-dev__pylint-5596</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>O(N^2) to O(N) config sync by batching _set_msg_status updates (0.372s to 0.026s)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="42" customHeight="1">
-      <c r="A82" s="2" t="n">
+    <row r="82">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13253</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>Column-by-column DataFrame processing to preserve per-column dtypes in categories_</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="42" customHeight="1">
-      <c r="A83" s="2" t="n">
+    <row r="83">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13243</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>SAG/SAGA native float32 support to avoid silent upcast to float64</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="42" customHeight="1">
-      <c r="A84" s="2" t="n">
+    <row r="84">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13186</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>0.20.3 maintenance release; speedup from fixing redundant double fit() in TransformedTargetRegressor</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="42" customHeight="1">
-      <c r="A85" s="2" t="n">
+    <row r="85">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13174</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Removes redundant forced-dtype validation from AdaBoost (Enhancement label)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="6" t="n">
+    <row r="86">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13151</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>New jaccard_score API replacing the behaviorally broken jaccard_similarity_score</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="2" t="n">
+    <row r="87">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-13124</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>Fixes StratifiedKFold regression where all classes got the same shuffle seed</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="42" customHeight="1">
-      <c r="A88" s="6" t="n">
+    <row r="88">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12989</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>Deprecation sentinel for NMF init parameter for API consistency</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="10" t="n">
+    <row r="89">
+      <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="11" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12931</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D89" s="13" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Manual sigmoid replaced with scipy.special.expit (explicit perf request #12914)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="42" customHeight="1">
-      <c r="A90" s="6" t="n">
+    <row r="90">
+      <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12859</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>SVC docstring reformatting only - no code changed</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="6" t="n">
+    <row r="91">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12822</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>Pure TfidfVectorizer docstring reformatting</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="42" customHeight="1">
-      <c r="A92" s="2" t="n">
+    <row r="92">
+      <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12760</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>Fixes division-by-zero in davies_bouldin_score; np.nanmax removal is incidental</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="42" customHeight="1">
-      <c r="A93" s="2" t="n">
+    <row r="93">
+      <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12701</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
         <is>
           <t>Precomputes VI/V once to fix n_jobs-dependent results regression</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="42" customHeight="1">
-      <c r="A94" s="2" t="n">
+    <row r="94">
+      <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12656</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>Deprecates labels param in hamming_loss; incidentally removes unique_labels() call</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="42" customHeight="1">
-      <c r="A95" s="2" t="n">
+    <row r="95">
+      <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12625</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>Fixes crash in check_array on pandas.Series</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="42" customHeight="1">
-      <c r="A96" s="6" t="n">
+    <row r="96">
+      <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12581</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>Corrects docstrings marking groups as optional - no-op delegation overrides</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="42" customHeight="1">
-      <c r="A97" s="2" t="n">
+    <row r="97">
+      <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12567</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>Fixes inverted version-check putting modern NumPy on slow frompyfunc path</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="42" customHeight="1">
-      <c r="A98" s="10" t="n">
+    <row r="98">
+      <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12543</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>IsolationForest uses prefer=threads to eliminate inter-process memory copies (issue #12469, Performance)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="42" customHeight="1">
-      <c r="A99" s="2" t="n">
+    <row r="99">
+      <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12514</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
         <is>
           <t>Fixes KBinsDiscretizer.transform calling fit_transform (thread-safety bug)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="6" t="n">
+    <row r="100">
+      <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12446</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
         <is>
           <t>Adds formula to StandardScaler docstring only</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="42" customHeight="1">
-      <c r="A101" s="2" t="n">
+    <row r="101">
+      <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12379</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>Fixes IncrementalPCA regression where final batch &lt; n_components</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="2" t="n">
+    <row r="102">
+      <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12246</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>Fixes fetch_openml() ignoring local cache entirely</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="42" customHeight="1">
-      <c r="A103" s="6" t="n">
+    <row r="103">
+      <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12230</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
         <is>
           <t>Removes unused variables flagged by static analysis</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="42" customHeight="1">
-      <c r="A104" s="6" t="n">
+    <row r="104">
+      <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12211</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
         <is>
           <t>Spelling correction: Harabaz to Harabasz in public API</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="42" customHeight="1">
-      <c r="A105" s="2" t="n">
+    <row r="105">
+      <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12172</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>Forces threading backend in Python 2.7 to fix pickling crash</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="42" customHeight="1">
-      <c r="A106" s="2" t="n">
+    <row r="106">
+      <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12155</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
         <is>
           <t>Replaces 'is warn' with '== warn' to fix multiprocessing failure</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="42" customHeight="1">
-      <c r="A107" s="6" t="n">
+    <row r="107">
+      <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12117</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>Docstring update for OneHotEncoder.fit_transform only</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="42" customHeight="1">
-      <c r="A108" s="10" t="n">
+    <row r="108">
+      <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-12116</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D108" s="13" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>MultiLabelBinarizer caches class_to_index dict (issue #11680, labeled Efficiency)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="42" customHeight="1">
-      <c r="A109" s="2" t="n">
+    <row r="109">
+      <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-11754</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>Moves ConvergenceWarning into Cython to fix silent non-convergence</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="6" t="n">
+    <row r="110">
+      <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-11674</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
         <is>
           <t>Introduces passthrough sentinel for Pipeline steps (API feature)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="6" t="n">
+    <row r="111">
+      <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-11526</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>Adds ChangedBehaviorWarning to LDA for invalid n_components</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="42" customHeight="1">
-      <c r="A112" s="6" t="n">
+    <row r="112">
+      <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-11364</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>Adds verbose parameter to Pipeline/FeatureUnion (feature)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="42" customHeight="1">
-      <c r="A113" s="6" t="n">
+    <row r="113">
+      <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>scikit-learn__scikit-learn-11179</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
         <is>
           <t>Adds multilabel_confusion_matrix (feature addition)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="42" customHeight="1">
-      <c r="A114" s="6" t="n">
+    <row r="114">
+      <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-12615</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>Downgrades logger.warning to logger.info to fix -W build failure</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="42" customHeight="1">
-      <c r="A115" s="2" t="n">
+    <row r="115">
+      <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-12598</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
         <is>
           <t>Fixes LaTeX crash for figures inside admonitions</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="42" customHeight="1">
-      <c r="A116" s="2" t="n">
+    <row r="116">
+      <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-11861</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>Expands _INVALID_BUILTIN_CLASSES to fix wrong __module__ in type hints</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="42" customHeight="1">
-      <c r="A117" s="6" t="n">
+    <row r="117">
+      <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-11489</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
         <is>
           <t>Adds linkcheck_anchors_ignore_for_url config option (feature)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="42" customHeight="1">
-      <c r="A118" s="6" t="n">
+    <row r="118">
+      <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-10807</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>Adds domain objects to table of contents (feature)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="42" customHeight="1">
-      <c r="A119" s="2" t="n">
+    <row r="119">
+      <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-9547</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>Replaces sequential keyword loop with precompiled regex to add GNU type support</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="42" customHeight="1">
-      <c r="A120" s="2" t="n">
+    <row r="120">
+      <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-6422</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>Fixes autosummary stub files not re-written after template changes</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="42" customHeight="1">
-      <c r="A121" s="2" t="n">
+    <row r="121">
+      <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>sphinx-doc__sphinx-8537</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>Broken memoization guard in ModuleAnalyzer.analyze() restored; ~71% speedup is incidental</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="42" customHeight="1">
-      <c r="A122" s="2" t="n">
+    <row r="122">
+      <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>sympy__sympy-14331</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>Fixes MatrixBase.exp() returning complex expressions for real-valued matrices</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="42" customHeight="1">
-      <c r="A123" s="2" t="n">
+    <row r="123">
+      <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>sympy__sympy-14278</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t>New closed-form |base**exponent| eval rule fixing incorrect/unsimplified Abs results</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="42" customHeight="1">
-      <c r="A124" s="2" t="n">
+    <row r="124">
+      <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>sympy__sympy-27666</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>Fixes ask(Q.infinite(I*oo)) returning None; speedup is incidental</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="42" customHeight="1">
-      <c r="A125" s="2" t="n">
+    <row r="125">
+      <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>sympy__sympy-27347</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>Adds specialized expectation for PoissonDistribution to fix precision errors</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="42" customHeight="1">
-      <c r="A126" s="2" t="n">
+    <row r="126">
+      <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>sympy__sympy-27085</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>Copies input rows in DDM.__init__ to fix caller-side mutation bug</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="42" customHeight="1">
-      <c r="A127" s="2" t="n">
+    <row r="127">
+      <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>sympy__sympy-26989</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>Returns unevaluated limits for AppliedUndef to fix wrong limit results</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="42" customHeight="1">
-      <c r="A128" s="2" t="n">
+    <row r="128">
+      <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>sympy__sympy-26940</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>Fixes type(tuple) bug in heurisch._iter_mappings that broke integral evaluation</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="42" customHeight="1">
-      <c r="A129" s="2" t="n">
+    <row r="129">
+      <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>sympy__sympy-26935</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>Fixes type-keying bug in heurisch permutation groups (regression #26922/#26930)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="42" customHeight="1">
-      <c r="A130" s="2" t="n">
+    <row r="130">
+      <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>sympy__sympy-26848</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
         <is>
           <t>Fixes incorrect exp(log(...)) auto-simplification in Gruntz algorithm</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="42" customHeight="1">
-      <c r="A131" s="2" t="n">
+    <row r="131">
+      <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>sympy__sympy-26693</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>Removes nsimplify from log._eval_nseries to fix incorrect series results</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="42" customHeight="1">
-      <c r="A132" s="2" t="n">
+    <row r="132">
+      <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>sympy__sympy-26546</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
         <is>
           <t>Adds early return False in Pow._eval_is_extended_real for n-th roots of non-real bases</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="42" customHeight="1">
-      <c r="A133" s="10" t="n">
+    <row r="133">
+      <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="11" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>sympy__sympy-26358</t>
         </is>
       </c>
-      <c r="C133" s="12" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D133" s="13" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Reduces permutation search space in heurisch() from n! to k! to fix near-infinite hang (#15498)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="42" customHeight="1">
-      <c r="A134" s="2" t="n">
+    <row r="134">
+      <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>sympy__sympy-26036</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
         <is>
           <t>Fixes NotImplementedError in Pow._eval_nseries with float coefficients</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="42" customHeight="1">
-      <c r="A135" s="10" t="n">
+    <row r="135">
+      <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="11" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>sympy__sympy-26004</t>
         </is>
       </c>
-      <c r="C135" s="12" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D135" s="13" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Caches trig/hyp inverse dictionaries via lazy init (commit: _invert_trig_hyp: cache dicts)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="42" customHeight="1">
-      <c r="A136" s="2" t="n">
+    <row r="136">
+      <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>sympy__sympy-25852</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>Fixes incorrect return values in atan/acot._eval_aseries near branch cuts</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="42" customHeight="1">
-      <c r="A137" s="2" t="n">
+    <row r="137">
+      <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>sympy__sympy-25758</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>Replaces im() with coeff(I) to fix incorrect over-triggering in inequality solver</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="42" customHeight="1">
-      <c r="A138" s="2" t="n">
+    <row r="138">
+      <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>sympy__sympy-25614</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>Fixes Float == Rational returning True; simplified __eq__ is faster as a consequence</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="42" customHeight="1">
-      <c r="A139" s="10" t="n">
+    <row r="139">
+      <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>sympy__sympy-25591</t>
         </is>
       </c>
-      <c r="C139" s="12" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Targeted optimization</t>
         </is>
       </c>
-      <c r="D139" s="13" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>Splits facts into number/matrix subsets to halve SAT solver input (issue #25533, perf request)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="42" customHeight="1">
-      <c r="A140" s="6" t="n">
+    <row r="140">
+      <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>sympy__sympy-25205</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Not a performance change</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
         <is>
           <t>Removes one incorrect docstring line from MatrixCalculus.diff</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="42" customHeight="1">
-      <c r="A141" s="2" t="n">
+    <row r="141">
+      <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>sympy__sympy-24665</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Side effect of bug fix</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
         <is>
           <t>defaultdict deduplication fixes factor_list() returning duplicate factor bases</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B1" s="18" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>Targeted optimization</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>11.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>Side effect of bug fix</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="n">
-        <v>80</v>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Ambiguous</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Not a performance change</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>30.7%</t>
         </is>
       </c>
     </row>
